--- a/MainTop/23.04.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/23.04.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.04.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F8F7D3-D871-434C-8AD7-9D42F342F103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2155F9A2-0379-4936-8BD2-3BCA0E874AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,10 +647,10 @@
   <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.5703125" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
